--- a/reports/history/build-4/Failed_Test_Cases.xlsx
+++ b/reports/history/build-4/Failed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t>Test ID</t>
   </si>
@@ -34,13 +34,13 @@
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_AUTH_027</t>
+    <t>TC_AUTH_006</t>
   </si>
   <si>
     <t>Authentication</t>
   </si>
   <si>
-    <t>Authentication Verification - Case 27</t>
+    <t>Authentication Verification - Case 6</t>
   </si>
   <si>
     <t>High</t>
@@ -49,64 +49,100 @@
     <t>FAILED</t>
   </si>
   <si>
-    <t>AssertionError: State mismatch on scenario index 26</t>
-  </si>
-  <si>
-    <t>TC_AZ_014</t>
-  </si>
-  <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>Authorization Verification - Case 14</t>
+    <t>AssertionError: State mismatch on scenario index 5</t>
+  </si>
+  <si>
+    <t>TC_AUTH_026</t>
+  </si>
+  <si>
+    <t>Authentication Verification - Case 26</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t>AssertionError: State mismatch on scenario index 53</t>
-  </si>
-  <si>
-    <t>TC_DASH_006</t>
-  </si>
-  <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
-    <t>Dashboard Verification - Case 6</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 145</t>
-  </si>
-  <si>
-    <t>TC_CRUD_015</t>
+    <t>AssertionError: State mismatch on scenario index 25</t>
+  </si>
+  <si>
+    <t>TC_NAV_004</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Navigation Verification - Case 4</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 113</t>
+  </si>
+  <si>
+    <t>TC_CRUD_028</t>
   </si>
   <si>
     <t>CRUD Operations</t>
   </si>
   <si>
-    <t>CRUD Operations Verification - Case 15</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 214</t>
-  </si>
-  <si>
-    <t>TC_CRUD_023</t>
-  </si>
-  <si>
-    <t>CRUD Operations Verification - Case 23</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 222</t>
-  </si>
-  <si>
-    <t>TC_CRUD_035</t>
-  </si>
-  <si>
-    <t>CRUD Operations Verification - Case 35</t>
-  </si>
-  <si>
-    <t>AssertionError: State mismatch on scenario index 234</t>
+    <t>CRUD Operations Verification - Case 28</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 227</t>
+  </si>
+  <si>
+    <t>TC_SRCH_008</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Search Verification - Case 8</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 247</t>
+  </si>
+  <si>
+    <t>TC_ACC_010</t>
+  </si>
+  <si>
+    <t>Accessibility</t>
+  </si>
+  <si>
+    <t>Accessibility Verification - Case 10</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 419</t>
+  </si>
+  <si>
+    <t>TC_REGR_018</t>
+  </si>
+  <si>
+    <t>Regression Suite</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 18</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 477</t>
+  </si>
+  <si>
+    <t>TC_REGR_020</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 20</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 479</t>
+  </si>
+  <si>
+    <t>TC_REGR_048</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 48</t>
+  </si>
+  <si>
+    <t>AssertionError: State mismatch on scenario index 507</t>
   </si>
 </sst>
 </file>
@@ -497,11 +533,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
@@ -548,7 +584,7 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -559,42 +595,42 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>138</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>247</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -611,13 +647,13 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
@@ -628,45 +664,114 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7">
-        <v>256</v>
+        <v>166</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>245</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>134</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10">
+        <v>123</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
